--- a/SoRoSim Robots/my_robot(2.00to1.25)(3tendon)/10-08-2025/Validation(2.00to1.25)(3tendon).xlsx
+++ b/SoRoSim Robots/my_robot(2.00to1.25)(3tendon)/10-08-2025/Validation(2.00to1.25)(3tendon).xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/SoRoSim Robots/my_robot(2.00to1.25)(3tendon)/10-08-2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2617" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{823B792D-E9DA-4C9A-B45E-037F8C64FF25}"/>
+  <xr:revisionPtr revIDLastSave="2638" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E3E04B2-8105-4C1A-A789-1E0ABDA0E745}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation (double)" sheetId="12" r:id="rId1"/>
     <sheet name="Distal Validati (double)" sheetId="19" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="26" r:id="rId3"/>
-    <sheet name="Conversion" sheetId="4" r:id="rId4"/>
+    <sheet name="Distal Vali (double non perp)" sheetId="27" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="26" r:id="rId4"/>
+    <sheet name="Conversion" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -79,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="38">
   <si>
     <t>Fx (N)</t>
   </si>
@@ -892,29 +893,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B763EDC-8536-442D-A8D3-F37978D4DE80}">
   <dimension ref="A1:AC18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="7.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>11</v>
       </c>
@@ -953,7 +954,7 @@
       <c r="AB1" s="25"/>
       <c r="AC1" s="26"/>
     </row>
-    <row r="2" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -1042,7 +1043,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>0.3</v>
       </c>
@@ -1139,7 +1140,7 @@
         <v>-0.16968383775705329</v>
       </c>
     </row>
-    <row r="4" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>0.4</v>
       </c>
@@ -1236,7 +1237,7 @@
         <v>6.9846011870356717E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>0.7</v>
       </c>
@@ -1333,7 +1334,7 @@
         <v>-3.5774078873262199E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>0.7</v>
       </c>
@@ -1430,7 +1431,7 @@
         <v>-0.11738587778127019</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>0.6</v>
       </c>
@@ -1527,7 +1528,7 @@
         <v>-1.8520203450577422E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>0.8</v>
       </c>
@@ -1624,7 +1625,7 @@
         <v>-5.542594283105548E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>0.3</v>
       </c>
@@ -1721,7 +1722,7 @@
         <v>5.8475902526015949E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>0.5</v>
       </c>
@@ -1818,7 +1819,7 @@
         <v>7.2511475698173899E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>0.4</v>
       </c>
@@ -1915,7 +1916,7 @@
         <v>1.4258336355669421E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>0.7</v>
       </c>
@@ -2012,7 +2013,7 @@
         <v>0.11017490691826692</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>0.3</v>
       </c>
@@ -2109,7 +2110,7 @@
         <v>2.6205596248324969E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>0.6</v>
       </c>
@@ -2206,7 +2207,7 @@
         <v>8.753144830914783E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>0.7</v>
       </c>
@@ -2303,7 +2304,7 @@
         <v>-0.12862977834001521</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>0.4</v>
       </c>
@@ -2400,7 +2401,7 @@
         <v>6.9869847527751716E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>0.8</v>
       </c>
@@ -2497,7 +2498,7 @@
         <v>5.6870872849057119E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.35">
       <c r="X18" s="17">
         <f>AVERAGE(X4:X17)</f>
         <v>-1.5408713342843674E-3</v>
@@ -2539,44 +2540,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309BE333-3BAE-4E8D-AF02-67A9E2013036}">
   <dimension ref="A1:AS17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" customWidth="1"/>
-    <col min="27" max="27" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.7265625" customWidth="1"/>
+    <col min="27" max="27" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.7265625" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="11" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>11</v>
       </c>
@@ -2633,7 +2634,7 @@
       <c r="AR1" s="29"/>
       <c r="AS1" s="29"/>
     </row>
-    <row r="2" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:45" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -2756,7 +2757,7 @@
       <c r="AR2" s="27"/>
       <c r="AS2" s="27"/>
     </row>
-    <row r="3" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:45" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
         <f>'Proximal Validation (double)'!A3</f>
         <v>0.3</v>
@@ -2921,7 +2922,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A4" s="14">
         <f>'Proximal Validation (double)'!A4</f>
         <v>0.4</v>
@@ -3094,7 +3095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <f>'Proximal Validation (double)'!A5</f>
         <v>0.7</v>
@@ -3245,7 +3246,7 @@
       <c r="AR5" s="27"/>
       <c r="AS5" s="27"/>
     </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <f>'Proximal Validation (double)'!A6</f>
         <v>0.7</v>
@@ -3400,7 +3401,7 @@
       <c r="AR6" s="8"/>
       <c r="AS6" s="8"/>
     </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <f>'Proximal Validation (double)'!A7</f>
         <v>0.6</v>
@@ -3558,7 +3559,7 @@
       <c r="AR7" s="8"/>
       <c r="AS7" s="8"/>
     </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <f>'Proximal Validation (double)'!A8</f>
         <v>0.8</v>
@@ -3699,7 +3700,7 @@
         <v>0.3543173457748785</v>
       </c>
     </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <f>'Proximal Validation (double)'!A9</f>
         <v>0.3</v>
@@ -3843,7 +3844,7 @@
       <c r="AM9" s="13"/>
       <c r="AN9" s="13"/>
     </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <f>'Proximal Validation (double)'!A10</f>
         <v>0.5</v>
@@ -3984,7 +3985,7 @@
         <v>5.5551180786501675E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <f>'Proximal Validation (double)'!A11</f>
         <v>0.4</v>
@@ -4128,7 +4129,7 @@
       <c r="AM11" s="13"/>
       <c r="AN11" s="13"/>
     </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <f>'Proximal Validation (double)'!A12</f>
         <v>0.7</v>
@@ -4269,7 +4270,7 @@
         <v>8.6974061820051185E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <f>'Proximal Validation (double)'!A13</f>
         <v>0.3</v>
@@ -4413,7 +4414,7 @@
       <c r="AM13" s="13"/>
       <c r="AN13" s="13"/>
     </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <f>'Proximal Validation (double)'!A14</f>
         <v>0.6</v>
@@ -4554,7 +4555,7 @@
         <v>2.4030642950857519</v>
       </c>
     </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <f>'Proximal Validation (double)'!A15</f>
         <v>0.7</v>
@@ -4695,7 +4696,7 @@
         <v>0.4975500671542139</v>
       </c>
     </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <f>'Proximal Validation (double)'!A16</f>
         <v>0.4</v>
@@ -4836,7 +4837,7 @@
         <v>0.6477108966008629</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <f>'Proximal Validation (double)'!A17</f>
         <v>0.8</v>
@@ -4993,11 +4994,1151 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A48A93BC-E2FF-455A-B8A4-E55141589AAB}">
+  <dimension ref="A1:AS8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.7265625" customWidth="1"/>
+    <col min="27" max="27" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ1" s="29"/>
+      <c r="AK1" s="29"/>
+      <c r="AL1" s="29"/>
+      <c r="AM1" s="29"/>
+      <c r="AN1" s="29"/>
+      <c r="AO1" s="29"/>
+      <c r="AP1" s="29"/>
+      <c r="AQ1" s="29"/>
+      <c r="AR1" s="29"/>
+      <c r="AS1" s="29"/>
+    </row>
+    <row r="2" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL2" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="AM2" s="27"/>
+      <c r="AN2" s="27"/>
+      <c r="AO2" s="27"/>
+      <c r="AP2" s="27"/>
+      <c r="AQ2" s="27"/>
+      <c r="AR2" s="27"/>
+      <c r="AS2" s="27"/>
+    </row>
+    <row r="3" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A3" s="14">
+        <f>'Proximal Validation (double)'!A4</f>
+        <v>0.4</v>
+      </c>
+      <c r="B3" s="14">
+        <f>'Proximal Validation (double)'!B4</f>
+        <v>0.1</v>
+      </c>
+      <c r="C3" s="14">
+        <f>'Proximal Validation (double)'!C4</f>
+        <v>1.57</v>
+      </c>
+      <c r="D3" s="14">
+        <f>'Proximal Validation (double)'!D4</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="E3" s="14">
+        <f>'Proximal Validation (double)'!E4</f>
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="14">
+        <f>'Proximal Validation (double)'!F4</f>
+        <v>0.06</v>
+      </c>
+      <c r="G3" s="14">
+        <f>'Proximal Validation (double)'!G4</f>
+        <v>4.7119999999999997</v>
+      </c>
+      <c r="H3" s="14">
+        <f>'Proximal Validation (double)'!H4</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="I3" s="14">
+        <f>'Proximal Validation (double)'!I4</f>
+        <v>0.8</v>
+      </c>
+      <c r="J3" s="14">
+        <f>'Proximal Validation (double)'!J4</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="14">
+        <f>'Proximal Validation (double)'!K4</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="14">
+        <f>'Proximal Validation (double)'!L4</f>
+        <v>-7.01924553140998E-4</v>
+      </c>
+      <c r="M3" s="14">
+        <f>'Proximal Validation (double)'!M4</f>
+        <v>-1.88952703028917E-2</v>
+      </c>
+      <c r="N3" s="14">
+        <f>'Proximal Validation (double)'!N4</f>
+        <v>6.5155932679772399E-4</v>
+      </c>
+      <c r="O3" s="14">
+        <f>'Proximal Validation (double)'!O4</f>
+        <v>-3.4051635302603201E-3</v>
+      </c>
+      <c r="P3" s="14">
+        <f>'Proximal Validation (double)'!P4</f>
+        <v>7.4966698884963998E-3</v>
+      </c>
+      <c r="Q3" s="14">
+        <f>'Proximal Validation (double)'!Q4</f>
+        <v>-3.05809658020735E-2</v>
+      </c>
+      <c r="R3" s="14">
+        <v>0.84334380262950415</v>
+      </c>
+      <c r="S3" s="14">
+        <v>4.2128241680068498E-2</v>
+      </c>
+      <c r="T3" s="14">
+        <v>1.6226687180787622</v>
+      </c>
+      <c r="U3" s="14">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="V3" s="14">
+        <v>0.87387020359936229</v>
+      </c>
+      <c r="W3" s="14">
+        <v>2.0000021686112718E-2</v>
+      </c>
+      <c r="X3" s="14">
+        <v>4.7711582142370732</v>
+      </c>
+      <c r="Y3" s="14">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="Z3" s="15">
+        <v>2.9750495653670798E-5</v>
+      </c>
+      <c r="AA3" s="14">
+        <f t="shared" ref="AA3:AH8" si="0">R3-A3</f>
+        <v>0.44334380262950412</v>
+      </c>
+      <c r="AB3" s="14">
+        <f t="shared" si="0"/>
+        <v>-5.7871758319931507E-2</v>
+      </c>
+      <c r="AC3" s="14">
+        <f t="shared" si="0"/>
+        <v>5.2668718078762167E-2</v>
+      </c>
+      <c r="AD3" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE3" s="14">
+        <f t="shared" si="0"/>
+        <v>0.37387020359936229</v>
+      </c>
+      <c r="AF3" s="14">
+        <f t="shared" si="0"/>
+        <v>-3.9999978313887283E-2</v>
+      </c>
+      <c r="AG3" s="14">
+        <f t="shared" si="0"/>
+        <v>5.9158214237073459E-2</v>
+      </c>
+      <c r="AH3" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI3" s="16">
+        <f t="shared" ref="AI3:AI8" si="1">AVERAGE(ABS(AA3),ABS(AE3))</f>
+        <v>0.40860700311443321</v>
+      </c>
+      <c r="AJ3" s="16">
+        <f t="shared" ref="AJ3:AK8" si="2">AVERAGE(ABS(AB3),ABS(AF3))</f>
+        <v>4.8935868316909395E-2</v>
+      </c>
+      <c r="AK3" s="16">
+        <f t="shared" si="2"/>
+        <v>5.5913466157917813E-2</v>
+      </c>
+      <c r="AL3" s="8" cm="1">
+        <f t="array" ref="AL3">AVERAGE(ABS(AA3:AA8))</f>
+        <v>0.22497636747765681</v>
+      </c>
+      <c r="AM3" s="8" cm="1">
+        <f t="array" ref="AM3">AVERAGE(ABS(AB3:AB8))</f>
+        <v>3.6133214160114648E-2</v>
+      </c>
+      <c r="AN3" s="8" cm="1">
+        <f t="array" ref="AN3">AVERAGE(ABS(AC3:AC8))</f>
+        <v>0.2934919182376301</v>
+      </c>
+      <c r="AO3" s="8" cm="1">
+        <f t="array" ref="AO3">AVERAGE(ABS(AD3:AD8))</f>
+        <v>0</v>
+      </c>
+      <c r="AP3" s="8" cm="1">
+        <f t="array" ref="AP3">AVERAGE(ABS(AE3:AE8))</f>
+        <v>0.20289106341374855</v>
+      </c>
+      <c r="AQ3" s="8" cm="1">
+        <f t="array" ref="AQ3">AVERAGE(ABS(AF3:AF8))</f>
+        <v>4.7164678901087657E-2</v>
+      </c>
+      <c r="AR3" s="8" cm="1">
+        <f t="array" ref="AR3">AVERAGE(ABS(AG3:AG8))</f>
+        <v>0.33240163973351794</v>
+      </c>
+      <c r="AS3" s="8" cm="1">
+        <f t="array" ref="AS3">AVERAGE(ABS(AH3:AH8))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A4" s="5">
+        <f>'Proximal Validation (double)'!A5</f>
+        <v>0.7</v>
+      </c>
+      <c r="B4" s="5">
+        <f>'Proximal Validation (double)'!B5</f>
+        <v>0.16</v>
+      </c>
+      <c r="C4" s="5">
+        <f>'Proximal Validation (double)'!C5</f>
+        <v>1.57</v>
+      </c>
+      <c r="D4" s="5">
+        <f>'Proximal Validation (double)'!D5</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="E4" s="5">
+        <f>'Proximal Validation (double)'!E5</f>
+        <v>0.7</v>
+      </c>
+      <c r="F4" s="5">
+        <f>'Proximal Validation (double)'!F5</f>
+        <v>0.02</v>
+      </c>
+      <c r="G4" s="5">
+        <f>'Proximal Validation (double)'!G5</f>
+        <v>4.7119999999999997</v>
+      </c>
+      <c r="H4" s="5">
+        <f>'Proximal Validation (double)'!H5</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="I4" s="5">
+        <f>'Proximal Validation (double)'!I5</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <f>'Proximal Validation (double)'!J5</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <f>'Proximal Validation (double)'!K5</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <f>'Proximal Validation (double)'!L5</f>
+        <v>-1.1449491139501301E-3</v>
+      </c>
+      <c r="M4" s="5">
+        <f>'Proximal Validation (double)'!M5</f>
+        <v>-8.78715589642525E-2</v>
+      </c>
+      <c r="N4" s="5">
+        <f>'Proximal Validation (double)'!N5</f>
+        <v>1.2581461342051599E-3</v>
+      </c>
+      <c r="O4" s="5">
+        <f>'Proximal Validation (double)'!O5</f>
+        <v>-0.259054124355316</v>
+      </c>
+      <c r="P4" s="5">
+        <f>'Proximal Validation (double)'!P5</f>
+        <v>1.61738991737366E-2</v>
+      </c>
+      <c r="Q4" s="5">
+        <f>'Proximal Validation (double)'!Q5</f>
+        <v>-0.101423710584641</v>
+      </c>
+      <c r="R4" s="5">
+        <v>0.73359897343064195</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0.15604988378254078</v>
+      </c>
+      <c r="T4" s="5">
+        <v>1.5760159623132888</v>
+      </c>
+      <c r="U4" s="5">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="V4" s="5">
+        <v>0.76939525868909397</v>
+      </c>
+      <c r="W4" s="5">
+        <v>2.0315189542474604E-2</v>
+      </c>
+      <c r="X4" s="5">
+        <v>4.7379763948827796</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="Z4" s="12">
+        <v>1.5206627919956749E-6</v>
+      </c>
+      <c r="AA4" s="5">
+        <f t="shared" si="0"/>
+        <v>3.3598973430641998E-2</v>
+      </c>
+      <c r="AB4" s="5">
+        <f t="shared" si="0"/>
+        <v>-3.9501162174592208E-3</v>
+      </c>
+      <c r="AC4" s="5">
+        <f t="shared" si="0"/>
+        <v>6.0159623132887141E-3</v>
+      </c>
+      <c r="AD4" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE4" s="5">
+        <f t="shared" si="0"/>
+        <v>6.9395258689094019E-2</v>
+      </c>
+      <c r="AF4" s="5">
+        <f t="shared" si="0"/>
+        <v>3.1518954247460387E-4</v>
+      </c>
+      <c r="AG4" s="5">
+        <f t="shared" si="0"/>
+        <v>2.5976394882779807E-2</v>
+      </c>
+      <c r="AH4" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="9">
+        <f t="shared" si="1"/>
+        <v>5.1497116059868009E-2</v>
+      </c>
+      <c r="AJ4" s="9">
+        <f t="shared" si="2"/>
+        <v>2.1326528799669123E-3</v>
+      </c>
+      <c r="AK4" s="9">
+        <f t="shared" si="2"/>
+        <v>1.5996178598034261E-2</v>
+      </c>
+      <c r="AL4" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM4" s="27"/>
+      <c r="AN4" s="27"/>
+      <c r="AO4" s="27"/>
+      <c r="AP4" s="27"/>
+      <c r="AQ4" s="27"/>
+      <c r="AR4" s="27"/>
+      <c r="AS4" s="27"/>
+    </row>
+    <row r="5" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A5" s="5">
+        <f>'Proximal Validation (double)'!A7</f>
+        <v>0.6</v>
+      </c>
+      <c r="B5" s="5">
+        <f>'Proximal Validation (double)'!B7</f>
+        <v>0.12</v>
+      </c>
+      <c r="C5" s="5">
+        <f>'Proximal Validation (double)'!C7</f>
+        <v>2.3559999999999999</v>
+      </c>
+      <c r="D5" s="5">
+        <f>'Proximal Validation (double)'!D7</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="E5" s="5">
+        <f>'Proximal Validation (double)'!E7</f>
+        <v>0.3</v>
+      </c>
+      <c r="F5" s="5">
+        <f>'Proximal Validation (double)'!F7</f>
+        <v>0.04</v>
+      </c>
+      <c r="G5" s="5">
+        <f>'Proximal Validation (double)'!G7</f>
+        <v>3.927</v>
+      </c>
+      <c r="H5" s="5">
+        <f>'Proximal Validation (double)'!H7</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="I5" s="5">
+        <f>'Proximal Validation (double)'!I7</f>
+        <v>0.4</v>
+      </c>
+      <c r="J5" s="5">
+        <f>'Proximal Validation (double)'!J7</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <f>'Proximal Validation (double)'!K7</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <f>'Proximal Validation (double)'!L7</f>
+        <v>-1.2948727235197999E-3</v>
+      </c>
+      <c r="M5" s="5">
+        <f>'Proximal Validation (double)'!M7</f>
+        <v>-6.0354080051183701E-2</v>
+      </c>
+      <c r="N5" s="5">
+        <f>'Proximal Validation (double)'!N7</f>
+        <v>-0.103492647409439</v>
+      </c>
+      <c r="O5" s="5">
+        <f>'Proximal Validation (double)'!O7</f>
+        <v>-0.120804071426392</v>
+      </c>
+      <c r="P5" s="5">
+        <f>'Proximal Validation (double)'!P7</f>
+        <v>-0.51357686519622803</v>
+      </c>
+      <c r="Q5" s="5">
+        <f>'Proximal Validation (double)'!Q7</f>
+        <v>0.20345818996429399</v>
+      </c>
+      <c r="R5" s="5">
+        <v>0.23107788967051263</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0.19988905717099678</v>
+      </c>
+      <c r="T5" s="5">
+        <v>1.2368049655145594</v>
+      </c>
+      <c r="U5" s="5">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="V5" s="5">
+        <v>0.59778291893374225</v>
+      </c>
+      <c r="W5" s="5">
+        <v>0.12176972145266707</v>
+      </c>
+      <c r="X5" s="5">
+        <v>3.1465650072096207</v>
+      </c>
+      <c r="Y5" s="5">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="Z5" s="12">
+        <v>4.7832563617822807E-6</v>
+      </c>
+      <c r="AA5" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.36892211032948735</v>
+      </c>
+      <c r="AB5" s="5">
+        <f t="shared" si="0"/>
+        <v>7.9889057170996786E-2</v>
+      </c>
+      <c r="AC5" s="5">
+        <f t="shared" si="0"/>
+        <v>-1.1191950344854404</v>
+      </c>
+      <c r="AD5" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE5" s="5">
+        <f t="shared" si="0"/>
+        <v>0.29778291893374226</v>
+      </c>
+      <c r="AF5" s="5">
+        <f t="shared" si="0"/>
+        <v>8.176972145266706E-2</v>
+      </c>
+      <c r="AG5" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.78043499279037931</v>
+      </c>
+      <c r="AH5" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI5" s="9">
+        <f t="shared" si="1"/>
+        <v>0.3333525146316148</v>
+      </c>
+      <c r="AJ5" s="9">
+        <f t="shared" si="2"/>
+        <v>8.0829389311831923E-2</v>
+      </c>
+      <c r="AK5" s="9">
+        <f t="shared" si="2"/>
+        <v>0.94981501363790988</v>
+      </c>
+      <c r="AL5" s="11">
+        <f>AVERAGE(AL3,AP3)</f>
+        <v>0.21393371544570267</v>
+      </c>
+      <c r="AM5" s="11">
+        <f t="shared" ref="AM5:AN5" si="3">AVERAGE(AM3,AQ3)</f>
+        <v>4.1648946530601152E-2</v>
+      </c>
+      <c r="AN5" s="11">
+        <f t="shared" si="3"/>
+        <v>0.31294677898557399</v>
+      </c>
+      <c r="AO5" s="8"/>
+      <c r="AP5" s="8"/>
+      <c r="AQ5" s="8"/>
+      <c r="AR5" s="8"/>
+      <c r="AS5" s="8"/>
+    </row>
+    <row r="6" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
+        <f>'Proximal Validation (double)'!A8</f>
+        <v>0.8</v>
+      </c>
+      <c r="B6" s="5">
+        <f>'Proximal Validation (double)'!B8</f>
+        <v>0.12</v>
+      </c>
+      <c r="C6" s="5">
+        <f>'Proximal Validation (double)'!C8</f>
+        <v>2.3559999999999999</v>
+      </c>
+      <c r="D6" s="5">
+        <f>'Proximal Validation (double)'!D8</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="E6" s="5">
+        <f>'Proximal Validation (double)'!E8</f>
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="5">
+        <f>'Proximal Validation (double)'!F8</f>
+        <v>0.06</v>
+      </c>
+      <c r="G6" s="5">
+        <f>'Proximal Validation (double)'!G8</f>
+        <v>3.927</v>
+      </c>
+      <c r="H6" s="5">
+        <f>'Proximal Validation (double)'!H8</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="I6" s="5">
+        <f>'Proximal Validation (double)'!I8</f>
+        <v>0.4</v>
+      </c>
+      <c r="J6" s="5">
+        <f>'Proximal Validation (double)'!J8</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <f>'Proximal Validation (double)'!K8</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <f>'Proximal Validation (double)'!L8</f>
+        <v>-1.53041677549481E-3</v>
+      </c>
+      <c r="M6" s="5">
+        <f>'Proximal Validation (double)'!M8</f>
+        <v>-5.8196127414703397E-2</v>
+      </c>
+      <c r="N6" s="5">
+        <f>'Proximal Validation (double)'!N8</f>
+        <v>-0.16341306269168901</v>
+      </c>
+      <c r="O6" s="5">
+        <f>'Proximal Validation (double)'!O8</f>
+        <v>-0.25818380713462802</v>
+      </c>
+      <c r="P6" s="5">
+        <f>'Proximal Validation (double)'!P8</f>
+        <v>-0.79976713657379195</v>
+      </c>
+      <c r="Q6" s="5">
+        <f>'Proximal Validation (double)'!Q8</f>
+        <v>0.14228719472885101</v>
+      </c>
+      <c r="R6" s="5">
+        <v>0.59476728724092365</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0.1691366531602953</v>
+      </c>
+      <c r="T6" s="5">
+        <v>2.632314083560181</v>
+      </c>
+      <c r="U6" s="5">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="V6" s="5">
+        <v>0.34727586410577121</v>
+      </c>
+      <c r="W6" s="5">
+        <v>2.0013010012491533E-2</v>
+      </c>
+      <c r="X6" s="5">
+        <v>3.4946793920104242</v>
+      </c>
+      <c r="Y6" s="5">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="Z6" s="12">
+        <v>8.1502539417363336E-6</v>
+      </c>
+      <c r="AA6" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.2052327127590764</v>
+      </c>
+      <c r="AB6" s="5">
+        <f t="shared" si="0"/>
+        <v>4.9136653160295307E-2</v>
+      </c>
+      <c r="AC6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.27631408356018117</v>
+      </c>
+      <c r="AD6" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE6" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.15272413589422879</v>
+      </c>
+      <c r="AF6" s="5">
+        <f t="shared" si="0"/>
+        <v>-3.9986989987508464E-2</v>
+      </c>
+      <c r="AG6" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.43232060798957583</v>
+      </c>
+      <c r="AH6" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="10">
+        <f t="shared" si="1"/>
+        <v>0.17897842432665259</v>
+      </c>
+      <c r="AJ6" s="10">
+        <f t="shared" si="2"/>
+        <v>4.4561821573901886E-2</v>
+      </c>
+      <c r="AK6" s="10">
+        <f t="shared" si="2"/>
+        <v>0.3543173457748785</v>
+      </c>
+    </row>
+    <row r="7" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A7" s="5">
+        <f>'Proximal Validation (double)'!A12</f>
+        <v>0.7</v>
+      </c>
+      <c r="B7" s="5">
+        <f>'Proximal Validation (double)'!B12</f>
+        <v>0.12</v>
+      </c>
+      <c r="C7" s="5">
+        <f>'Proximal Validation (double)'!C12</f>
+        <v>3.927</v>
+      </c>
+      <c r="D7" s="5">
+        <f>'Proximal Validation (double)'!D12</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="E7" s="5">
+        <f>'Proximal Validation (double)'!E12</f>
+        <v>0.7</v>
+      </c>
+      <c r="F7" s="5">
+        <f>'Proximal Validation (double)'!F12</f>
+        <v>0.08</v>
+      </c>
+      <c r="G7" s="5">
+        <f>'Proximal Validation (double)'!G12</f>
+        <v>3.927</v>
+      </c>
+      <c r="H7" s="5">
+        <f>'Proximal Validation (double)'!H12</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="I7" s="5">
+        <f>'Proximal Validation (double)'!I12</f>
+        <v>1.2</v>
+      </c>
+      <c r="J7" s="5">
+        <f>'Proximal Validation (double)'!J12</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <f>'Proximal Validation (double)'!K12</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <f>'Proximal Validation (double)'!L12</f>
+        <v>-3.7175370380282402E-3</v>
+      </c>
+      <c r="M7" s="5">
+        <f>'Proximal Validation (double)'!M12</f>
+        <v>0.17499575018882799</v>
+      </c>
+      <c r="N7" s="5">
+        <f>'Proximal Validation (double)'!N12</f>
+        <v>-0.20276136696338701</v>
+      </c>
+      <c r="O7" s="5">
+        <f>'Proximal Validation (double)'!O12</f>
+        <v>-0.35743337869644198</v>
+      </c>
+      <c r="P7" s="5">
+        <f>'Proximal Validation (double)'!P12</f>
+        <v>-1.01576912403107</v>
+      </c>
+      <c r="Q7" s="5">
+        <f>'Proximal Validation (double)'!Q12</f>
+        <v>-0.85049569606780995</v>
+      </c>
+      <c r="R7" s="5">
+        <v>0.60708386291897221</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0.13750315316568468</v>
+      </c>
+      <c r="T7" s="5">
+        <v>3.9379232854293447</v>
+      </c>
+      <c r="U7" s="5">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="V7" s="5">
+        <v>0.77113358577284863</v>
+      </c>
+      <c r="W7" s="5">
+        <v>7.9383123564409214E-2</v>
+      </c>
+      <c r="X7" s="5">
+        <v>3.7639751617892423</v>
+      </c>
+      <c r="Y7" s="5">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="Z7" s="12">
+        <v>4.1565535988806004E-5</v>
+      </c>
+      <c r="AA7" s="5">
+        <f t="shared" si="0"/>
+        <v>-9.291613708102775E-2</v>
+      </c>
+      <c r="AB7" s="5">
+        <f t="shared" si="0"/>
+        <v>1.7503153165684682E-2</v>
+      </c>
+      <c r="AC7" s="5">
+        <f t="shared" si="0"/>
+        <v>1.092328542934462E-2</v>
+      </c>
+      <c r="AD7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE7" s="5">
+        <f t="shared" si="0"/>
+        <v>7.1133585772848673E-2</v>
+      </c>
+      <c r="AF7" s="5">
+        <f t="shared" si="0"/>
+        <v>-6.1687643559078797E-4</v>
+      </c>
+      <c r="AG7" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.16302483821075775</v>
+      </c>
+      <c r="AH7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="9">
+        <f t="shared" si="1"/>
+        <v>8.2024861426938211E-2</v>
+      </c>
+      <c r="AJ7" s="9">
+        <f t="shared" si="2"/>
+        <v>9.0600148006377348E-3</v>
+      </c>
+      <c r="AK7" s="9">
+        <f t="shared" si="2"/>
+        <v>8.6974061820051185E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
+        <f>'Proximal Validation (double)'!A17</f>
+        <v>0.8</v>
+      </c>
+      <c r="B8" s="5">
+        <f>'Proximal Validation (double)'!B17</f>
+        <v>0.2</v>
+      </c>
+      <c r="C8" s="5">
+        <f>'Proximal Validation (double)'!C17</f>
+        <v>4.7119999999999997</v>
+      </c>
+      <c r="D8" s="5">
+        <f>'Proximal Validation (double)'!D17</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="E8" s="5">
+        <f>'Proximal Validation (double)'!E17</f>
+        <v>0.3</v>
+      </c>
+      <c r="F8" s="5">
+        <f>'Proximal Validation (double)'!F17</f>
+        <v>0.02</v>
+      </c>
+      <c r="G8" s="5">
+        <f>'Proximal Validation (double)'!G17</f>
+        <v>4.7119999999999997</v>
+      </c>
+      <c r="H8" s="5">
+        <f>'Proximal Validation (double)'!H17</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="I8" s="5">
+        <f>'Proximal Validation (double)'!I17</f>
+        <v>0.8</v>
+      </c>
+      <c r="J8" s="5">
+        <f>'Proximal Validation (double)'!J17</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <f>'Proximal Validation (double)'!K17</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <f>'Proximal Validation (double)'!L17</f>
+        <v>-1.16670653223991E-2</v>
+      </c>
+      <c r="M8" s="5">
+        <f>'Proximal Validation (double)'!M17</f>
+        <v>0.23207890987396201</v>
+      </c>
+      <c r="N8" s="5">
+        <f>'Proximal Validation (double)'!N17</f>
+        <v>-1.73678714782E-2</v>
+      </c>
+      <c r="O8" s="5">
+        <f>'Proximal Validation (double)'!O17</f>
+        <v>-0.68982279300689697</v>
+      </c>
+      <c r="P8" s="5">
+        <f>'Proximal Validation (double)'!P17</f>
+        <v>-0.124690353870392</v>
+      </c>
+      <c r="Q8" s="5">
+        <f>'Proximal Validation (double)'!Q17</f>
+        <v>-0.78086811304092396</v>
+      </c>
+      <c r="R8" s="5">
+        <v>0.59415553136379651</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0.19155145307367963</v>
+      </c>
+      <c r="T8" s="5">
+        <v>5.0078344255587632</v>
+      </c>
+      <c r="U8" s="5">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="V8" s="5">
+        <v>0.55244027759321523</v>
+      </c>
+      <c r="W8" s="5">
+        <v>0.14029931767439774</v>
+      </c>
+      <c r="X8" s="5">
+        <v>4.1785052097094582</v>
+      </c>
+      <c r="Y8" s="5">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="Z8" s="12">
+        <v>5.3594381245624448E-5</v>
+      </c>
+      <c r="AA8" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.20584446863620354</v>
+      </c>
+      <c r="AB8" s="5">
+        <f t="shared" si="0"/>
+        <v>-8.4485469263203827E-3</v>
+      </c>
+      <c r="AC8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.29583442555876349</v>
+      </c>
+      <c r="AD8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.25244027759321525</v>
+      </c>
+      <c r="AF8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.12029931767439773</v>
+      </c>
+      <c r="AG8" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.53349479029054159</v>
+      </c>
+      <c r="AH8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="9">
+        <f t="shared" si="1"/>
+        <v>0.22914237311470939</v>
+      </c>
+      <c r="AJ8" s="9">
+        <f t="shared" si="2"/>
+        <v>6.4373932300359066E-2</v>
+      </c>
+      <c r="AK8" s="9">
+        <f t="shared" si="2"/>
+        <v>0.41466460792465254</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="AL4:AS4"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="R1:Z1"/>
+    <mergeCell ref="AA1:AH1"/>
+    <mergeCell ref="AI1:AS1"/>
+    <mergeCell ref="AL2:AS2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFC3D7D9-740E-4BB1-A5C5-EC42A3C8479B}">
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1">
         <v>-4.30593034252524E-4</v>
       </c>
@@ -5026,7 +6167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>-7.01924553140998E-4</v>
       </c>
@@ -5055,7 +6196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>-1.1449491139501301E-3</v>
       </c>
@@ -5084,7 +6225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>6.4405519515275999E-3</v>
       </c>
@@ -5113,7 +6254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>-1.2948727235197999E-3</v>
       </c>
@@ -5142,7 +6283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>-1.53041677549481E-3</v>
       </c>
@@ -5171,7 +6312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1.2701484374702001E-3</v>
       </c>
@@ -5200,7 +6341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>-6.7927502095699299E-4</v>
       </c>
@@ -5229,7 +6370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>-1.88525998964906E-3</v>
       </c>
@@ -5258,7 +6399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>-3.7175370380282402E-3</v>
       </c>
@@ -5287,7 +6428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>-2.49816104769707E-4</v>
       </c>
@@ -5316,7 +6457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>-1.3586492277681799E-3</v>
       </c>
@@ -5345,7 +6486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>-1.34865380823612E-3</v>
       </c>
@@ -5374,7 +6515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>-2.75324238464236E-3</v>
       </c>
@@ -5403,7 +6544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>-1.16670653223991E-2</v>
       </c>
@@ -5437,12 +6578,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048D6981-73D2-4F8C-88D7-D5FA77AC2EB0}">
   <dimension ref="A1:M18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="32" t="s">
         <v>21</v>
       </c>
@@ -5460,7 +6601,7 @@
       <c r="L1" s="33"/>
       <c r="M1" s="34"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
@@ -5498,7 +6639,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>0.112474009394646</v>
       </c>
@@ -5542,7 +6683,7 @@
         <v>0.112474009394646</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>-3.05809658020735E-2</v>
       </c>
@@ -5586,7 +6727,7 @@
         <v>-3.05809658020735E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>-0.101423710584641</v>
       </c>
@@ -5630,7 +6771,7 @@
         <v>-0.101423710584641</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>0.27253100275993303</v>
       </c>
@@ -5674,7 +6815,7 @@
         <v>0.27253100275993303</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>0.20345818996429399</v>
       </c>
@@ -5718,7 +6859,7 @@
         <v>0.20345818996429399</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>0.14228719472885101</v>
       </c>
@@ -5762,7 +6903,7 @@
         <v>0.14228719472885101</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>-0.22458755970001201</v>
       </c>
@@ -5806,7 +6947,7 @@
         <v>-0.22458755970001201</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>-0.42087453603744501</v>
       </c>
@@ -5850,7 +6991,7 @@
         <v>-0.42087453603744501</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>-0.26614278554916398</v>
       </c>
@@ -5894,7 +7035,7 @@
         <v>-0.26614278554916398</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>-0.85049569606780995</v>
       </c>
@@ -5938,7 +7079,7 @@
         <v>-0.85049569606780995</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>-0.98430818319320701</v>
       </c>
@@ -5982,7 +7123,7 @@
         <v>-0.98430818319320701</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>-0.62923872470855702</v>
       </c>
@@ -6026,7 +7167,7 @@
         <v>-0.62923872470855702</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>-0.65422439575195301</v>
       </c>
@@ -6070,7 +7211,7 @@
         <v>-0.65422439575195301</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>-0.82157814502716098</v>
       </c>
@@ -6114,7 +7255,7 @@
         <v>-0.82157814502716098</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>-0.80446076393127397</v>
       </c>
@@ -6158,7 +7299,7 @@
         <v>-0.80446076393127397</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>-0.78086811304092396</v>
       </c>
@@ -6212,20 +7353,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6482,6 +7623,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
@@ -6494,14 +7643,6 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
